--- a/baselines/svm-baseline/predicted_events_svm.xlsx
+++ b/baselines/svm-baseline/predicted_events_svm.xlsx
@@ -413,21 +413,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:B175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>time_s</t>
+        </is>
+      </c>
       <c r="B1" t="inlineStr">
-        <is>
-          <t>time_start</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>time_end</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
         <is>
           <t>eID</t>
         </is>
@@ -435,143 +430,89 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
-      </c>
-      <c r="B2" t="n">
-        <v>210.25</v>
-      </c>
-      <c r="C2" t="n">
-        <v>213.2</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>eID_1</t>
+        <v>211.9</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="n">
-        <v>213.65</v>
-      </c>
-      <c r="C3" t="n">
-        <v>214.75</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>eID_1</t>
+        <v>211.95</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="n">
-        <v>215.7</v>
-      </c>
-      <c r="C4" t="n">
-        <v>217</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>eID_1</t>
+        <v>212.7</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="n">
-        <v>217.5</v>
-      </c>
-      <c r="C5" t="n">
-        <v>218.75</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>eID_3</t>
+        <v>212.85</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="n">
-        <v>221.6</v>
-      </c>
-      <c r="C6" t="n">
-        <v>222.7</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>eID_3</t>
+        <v>212.9</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="n">
-        <v>223.1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>224.8</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>eID_1</t>
+        <v>212.95</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="n">
-        <v>227.35</v>
-      </c>
-      <c r="C8" t="n">
-        <v>229</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>eID_3</t>
+        <v>213.1</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="n">
-        <v>229.05</v>
-      </c>
-      <c r="C9" t="n">
-        <v>231.6</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>eID_1</t>
+        <v>213.15</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="n">
-        <v>231.65</v>
-      </c>
-      <c r="C10" t="n">
-        <v>233</v>
-      </c>
-      <c r="D10" t="inlineStr">
+        <v>213.4</v>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>eID_2</t>
         </is>
@@ -579,177 +520,1651 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="n">
-        <v>236.75</v>
-      </c>
-      <c r="C11" t="n">
-        <v>238.4</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>eID_3</t>
+        <v>216.65</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="n">
-        <v>243.35</v>
-      </c>
-      <c r="C12" t="n">
-        <v>244.6</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>eID_3</t>
+        <v>224.5</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" t="n">
-        <v>250.65</v>
-      </c>
-      <c r="C13" t="n">
-        <v>254.95</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>eID_2</t>
+        <v>231.9</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>eID_5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" t="n">
-        <v>259.5</v>
-      </c>
-      <c r="C14" t="n">
-        <v>260.5</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>eID_3</t>
+        <v>231.95</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>eID_5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="n">
-        <v>261.35</v>
-      </c>
-      <c r="C15" t="n">
-        <v>262.6</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>eID_3</t>
+        <v>232.05</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>eID_5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="n">
-        <v>262.7</v>
-      </c>
-      <c r="C16" t="n">
-        <v>263.7</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>eID_3</t>
+        <v>232.15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>eID_5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="n">
-        <v>269.55</v>
-      </c>
-      <c r="C17" t="n">
-        <v>270.85</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>eID_3</t>
+        <v>232.2</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>eID_5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="n">
-        <v>273.85</v>
-      </c>
-      <c r="C18" t="n">
-        <v>275.85</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>eID_2</t>
+        <v>232.25</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>eID_5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="n">
-        <v>281.4</v>
-      </c>
-      <c r="C19" t="n">
-        <v>283.6</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>eID_3</t>
+        <v>232.3</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>eID_5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="n">
-        <v>291.2</v>
-      </c>
-      <c r="C20" t="n">
-        <v>292.35</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>eID_2</t>
+        <v>232.35</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>eID_5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="n">
-        <v>293.35</v>
-      </c>
-      <c r="C21" t="n">
-        <v>297.55</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>eID_1</t>
+        <v>232.4</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>247.75</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>247.95</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>249.05</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>250.05</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>250.15</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>250.8</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>250.85</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>250.9</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>250.95</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>251</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>251.25</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>251.3</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>251.35</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>251.4</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>251.45</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>251.5</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>251.55</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>251.6</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>251.65</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>251.7</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>251.75</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>251.85</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>251.95</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>252</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>252.05</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>252.1</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>252.15</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>252.2</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>252.25</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>252.85</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>253.2</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>253.4</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>253.75</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>253.95</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>254</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>254.15</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>254.2</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>254.25</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>254.3</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>254.35</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>254.4</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>254.45</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>255.1</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>255.15</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>255.25</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>255.35</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>255.4</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>255.45</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>255.5</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>255.55</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>255.6</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>256.4</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>264.8</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>265.05</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>265.2</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>266.7</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>274.75</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>274.85</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>274.9</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>275</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>275.2</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>275.25</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>275.3</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>275.35</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>275.4</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>275.45</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>275.5</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>275.6</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>275.65</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>275.7</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>277.25</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>277.5</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>277.6</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>277.75</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>278.05</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>278.1</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>278.15</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>278.2</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>278.25</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>278.3</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>278.35</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>278.45</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>278.5</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>278.65</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>278.75</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>278.85</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>278.9</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>278.95</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>279</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>279.05</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>279.1</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>279.15</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>279.2</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>279.25</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>279.3</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>279.5</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>279.55</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>279.6</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>279.65</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>279.7</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>279.75</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>279.8</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>279.9</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>280</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>280.05</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>280.1</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>280.15</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>280.45</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>281</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>285.25</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>286.15</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>287</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>287.1</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>287.15</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>287.2</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>287.25</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>293.95</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>294.25</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>294.3</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>294.35</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>294.45</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>294.55</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>294.6</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>294.65</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>294.7</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>294.75</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>294.8</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>294.85</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>294.9</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>294.95</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>295.1</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>295.15</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>295.2</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>295.25</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>295.4</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>295.45</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>295.5</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>295.7</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>295.75</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>295.8</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>295.9</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>295.95</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>296.05</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>296.1</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>296.35</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>297.65</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>297.7</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>297.75</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>297.9</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>297.95</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>298</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>298.5</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>298.65</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>298.85</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
